--- a/tubingi-plan.xlsx
+++ b/tubingi-plan.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Комплект" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Звонки'!$A$5:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Звонки'!$A$5:$K$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Вопросы'!$A$5:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,16 +870,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -926,21 +930,41 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Телефон и почта</t>
+          <t>Телефон</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Кого звать</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Адрес и оговорки</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>Что спросить первым</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Дозвонился</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Ответ</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="92" customHeight="1">
+    <row r="6" ht="86" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Целевой</t>
@@ -948,28 +972,44 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ООО «ТПК Брик» Самара</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
+          <t>ООО «ТПК Брик»</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Самара</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Два передела на одной площадке. Фрезерный: портальный HV2514, ЧПУ Fanuc, стол 2500 × 1200 мм, заготовка до 6000 кг , точность ±0,015 мм. По ширине впритык: деталь 1150 при столе 1200 — запас 25 мм на сторону, а приспособление с прижимами по контуру (1270 мм) туда уже не встаёт. Расточный: Skoda W-160G, стол от 2200 × 2200 мм, ход по X 6000 мм, пиноль Ø160 с вылетом 1250 мм, соосность до 0,03 мм; плюс 2620Б со столом 1120 × 1250 и массой до 3000 кг</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Фрезерное направление +7 (846) 202-07-45 Расточное +7 (846) 203-07-17 info@tpkbrik.ru Пн–Пт 08:00–17:00</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+          <t>Два передела на одной площадке. Фрезерный: портальный HV2514, ЧПУ Fanuc, стол 2500 × 1200 мм, заготовка до 6000 кг, точность ±0,015 мм. По ширине впритык: деталь 1150 при столе 1200 — запас 25 мм на сторону, а приспособление с прижимами по контуру (1270 мм) туда уже не встаёт. Расточный: Skoda W-160G, стол от 2200 × 2200 мм, ход по X 6000 мм, пиноль Ø160 с вылетом 1250 мм, соосность до 0,03 мм; плюс 2620Б со столом 1120 × 1250 и массой до 3000 кг</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Фрезерное направление: +7 (846) 202-07-45 · Расточное: +7 (846) 203-07-17</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>info@tpkbrik.ru</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Пн–Пт 08:00–17:00</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Сколько деталей в месяц и в сколько смен. И отдельно: на фрезерном стол 1200 мм при нашей ширине 1150 — спросить, можно ли прижимать только по торцам. По массе вопросов нет, запас четырёхкратный. Расточная Skoda 2200 × 2200 берёт деталь с приспособлением свободно</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="92" customHeight="1">
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="86" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Уточнить</t>
@@ -977,28 +1017,48 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ООО «Тулапрессмаш» Тула, марка STEIF</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
+          <t>ООО «Тулапрессмаш»</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Тула, марка STEIF</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Портальный AWEA LP4025YZF : стол 4020 × 2400 мм, ходы 4000 / 3200 / 1000 мм, между колоннами 2700 мм, сменная горизонтальная головка с вращением 360° шагом 5° — прямо под радиальные борта. Плюс горизонтальный 2Б6180ГМФ4 со столом 1800 × 2200 мм и поворотным столом: сверление, зенкерование и резьба метчиком на одном станке. Подходящих станка два, а не три: у третьего, портального TDG-Е-SF 2116, стол 2000 × 1500 мм — деталь длиной 2083 мм на него не ложится, не хватает 83 мм, и ход по X 2100 мм этого не меняет</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>8 (800) 444-65-61 info@tulpm.ru Директор Ашпин Николай Анатольевич Тула, ул. Демидовская, 67</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+          <t>Портальный AWEA LP4025YZF: стол 4020 × 2400 мм, ходы 4000 / 3200 / 1000 мм, между колоннами 2700 мм, сменная горизонтальная головка с вращением 360° шагом 5° — прямо под радиальные борта. Плюс горизонтальный 2Б6180ГМФ4 со столом 1800 × 2200 мм и поворотным столом: сверление, зенкерование и резьба метчиком на одном станке. Подходящих станка два, а не три: у третьего, портального TDG-Е-SF 2116, стол 2000 × 1500 мм — деталь длиной 2083 мм на него не ложится, не хватает 83 мм, и ход по X 2100 мм этого не меняет</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>8 (800) 444-65-61</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>info@tulpm.ru</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Директор Ашпин Николай Анатольевич</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Тула, ул. Демидовская, 67</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Грузоподъёмность стола — она не опубликована ни для одного станка, поэтому 1895 кг ничем не подтверждены. И условия оплаты: у них налоговый долг около 3 млн ₽, работать по факту сдачи</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="92" customHeight="1">
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="86" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Уточнить</t>
@@ -1006,28 +1066,40 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ООО «Металлист-Тольятти» Тольятти</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
+          <t>ООО «Металлист-Тольятти»</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Тольятти</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Фрезерная и расточная с ЧПУ: 6000 × 2000 × 1250 мм. Станки Coburg PMC3000, MAHO-1600, Okuma MCM16</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>+7 (903) 302-53-97 , +7 (937) 211-31-77 office.metall-tlt@yandex.ru taa@metallist-tlt.ru</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>+7 (903) 302-53-97, +7 (937) 211-31-77</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>office.metall-tlt@yandex.ru · taa@metallist-tlt.ru</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Грузоподъёмность стола — по массе на сайте нет ни одной цифры. И чьё оборудование: основных средств у них 27,5 млн ₽, площадка, похоже, арендованная</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="92" customHeight="1">
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="86" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Запасной</t>
@@ -1035,28 +1107,40 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ООО «Завод РТО» Оренбург</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr"/>
+          <t>ООО «Завод РТО»</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Оренбург</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Расточной Wotan Rapid 3 с ЧПУ, поворотный стол 3000 × 2000 мм, деталь до 2 м высотой и до 2 тонн . Но на той же странице завод объявляет по крупногабариту массу до 25 тонн и габариты до 4000 × 4000 × 4000 мм, не называя станка. Точность заявлена до ±0,01–0,05 мм</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>+7 (3532) 44-15-45 , +7 (3532) 44-15-47 ozrto.ru</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+          <t>Расточной Wotan Rapid 3 с ЧПУ, поворотный стол 3000 × 2000 мм, деталь до 2 м высотой и до 2 тонн. Но на той же странице завод объявляет по крупногабариту массу до 25 тонн и габариты до 4000 × 4000 × 4000 мм, не называя станка. Точность заявлена до ±0,01–0,05 мм</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>+7 (3532) 44-15-45, +7 (3532) 44-15-47</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>ozrto.ru</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>На чём делаете детали тяжелее двух тонн. Наша деталь 1895 кг на Wotan проходит, а с приспособлением около 3000 кг — уже нет. Если 25 тонн относятся к другому станку, надо знать к какому</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="92" customHeight="1">
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="86" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Уточнить</t>
@@ -1064,28 +1148,44 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ООО «МСЗ-Механика» Электросталь</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr"/>
+          <t>ООО «МСЗ-Механика»</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Электросталь</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Фрезерно-расточной с ЧПУ МС625МФ : деталь до 6000 × 2500 × 1000 мм. Парк более 60 станков . И главное: они сами делают оснастку — приспособления, кондуктора, мерительный инструмент. Есть термообработка</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>8 (496) 577-60-26 , 8 (496) 577-67-37 mszm@mail.ru Директор Чурин Андрей Владимирович Отдел закупок +7 (496) 577-31-52</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Возьмут ли гражданский заказ со стороны — это контур Росатома, есть пропускной режим. И грузоподъёмность стола МС625МФ : ограничений по массе на странице нет. Взамен они сами делают оснастку — приспособление можно заказать у них же</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="92" customHeight="1">
+          <t>Фрезерно-расточной с ЧПУ МС625МФ: деталь до 6000 × 2500 × 1000 мм. Парк более 60 станков. И главное: они сами делают оснастку — приспособления, кондуктора, мерительный инструмент. Есть термообработка</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>8 (496) 577-60-26, 8 (496) 577-67-37 · Отдел закупок: +7 (496) 577-31-52</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>mszm@mail.ru</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Директор Чурин Андрей Владимирович</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Возьмут ли гражданский заказ со стороны — это контур Росатома, есть пропускной режим. И грузоподъёмность стола МС625МФ: ограничений по массе на странице нет. Взамен они сами делают оснастку — приспособление можно заказать у них же</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="86" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Целевой</t>
@@ -1093,28 +1193,44 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ОАО «ЭЗТМ» Электросталь</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
+          <t>ОАО «ЭЗТМ»</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Электросталь</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Фрезерные с ЧПУ: изделие до 8500 × 2500 × 2500 мм, вес до 65 тонн . Расточные с ЧПУ: до 12 000 × 5600 × 4000 мм, 60 тонн. Глубокое сверление Ø до 120 мм — ровно наше нагнетательное отверстие. Всего около 450 металлорежущих станков</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>+7 (496) 577-72-46 , +7 (495) 702-97-57 eztm@eztm.ru Запрос — на имя коммерческого директора на бланке</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
+          <t>Фрезерные с ЧПУ: изделие до 8500 × 2500 × 2500 мм, вес до 65 тонн. Расточные с ЧПУ: до 12 000 × 5600 × 4000 мм, 60 тонн. Глубокое сверление Ø до 120 мм — ровно наше нагнетательное отверстие. Всего около 450 металлорежущих станков</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>+7 (496) 577-72-46, +7 (495) 702-97-57</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>eztm@eztm.ru</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Запрос — на имя коммерческого директора на бланке</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Берут ли работу со стороны и на каком станке пойдёт наша плита</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="92" customHeight="1">
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="86" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Уточнить</t>
@@ -1122,28 +1238,36 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ООО «СММ-ТяжМаш» Сосновый Бор</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
+          <t>ООО «СММ-ТяжМаш»</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Сосновый Бор</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Расточной PAMA SPEEDRAM 4000 + TM100, поворотный стол 4000 × 4000 мм, 100 тонн . Фрезерная группа мелкая — работа пойдёт на расточном</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Телефон на сайте не опубликован — через форму на smmtm.ru ИНН 4726003707 Сосновый Бор, ул. Мира, 1</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
+          <t>Расточной PAMA SPEEDRAM 4000 + TM100, поворотный стол 4000 × 4000 мм, 100 тонн. Фрезерная группа мелкая — работа пойдёт на расточном</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Телефон на сайте не опубликован — через форму на smmtm.ru · ИНН 4726003707 · Сосновый Бор, ул. Мира, 1</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Как на расточном получить плоскости бортов. И возьмут ли гражданский заказ</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="92" customHeight="1">
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="86" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Уточнить</t>
@@ -1151,28 +1275,44 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЗМО №1» Лысьва</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr"/>
+          <t>ООО «ЗМО №1»</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Лысьва</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Портально-фрезерные с ЧПУ PM3080HZ (до 8000 × 3500 мм, 40 т) и PM2040HA (4000 × 2500 мм, 20 т)</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>+7 (34249) 390-11 , +7 (342) 258-00-68 egorova@zmo1.ru Директор Егоров Ярослав Витальевич</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>+7 (34249) 390-11, +7 (342) 258-00-68</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>egorova@zmo1.ru</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Директор Егоров Ярослав Витальевич</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Чьи станки: у юрлица основных средств 26,1 млн ₽, а два портала стоят кратно больше</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="92" customHeight="1">
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="86" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Уточнить</t>
@@ -1180,28 +1320,40 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ООО ПК «НТМЗ» Нижний Тагил</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
+          <t>ООО ПК «НТМЗ»</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Тагил</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Портальный KAFO BMC-4122, стол 4000 × 2100 мм. И более сильный YSM 7030 : стол 6600 × 2400 мм, ходы 7000 / 3000 / 1500 мм, детали до 25 тонн , введён в апреле 2026. Чугун назван прямо: «корпусные детали из чугуна и стали весом до 10 тонн»</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>+7 (343) 592-90-21 , +7 (343) 592-90-22 info@ntmzpk.ru, office@ntmzpk.ru</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+          <t>Портальный KAFO BMC-4122, стол 4000 × 2100 мм. И более сильный YSM 7030: стол 6600 × 2400 мм, ходы 7000 / 3000 / 1500 мм, детали до 25 тонн, введён в апреле 2026. Чугун назван прямо: «корпусные детали из чугуна и стали весом до 10 тонн»</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>+7 (343) 592-90-21, +7 (343) 592-90-22</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>info@ntmzpk.ru · office@ntmzpk.ru</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>На чьём балансе станок: у самого юрлица основных средств 4,7 млн ₽. Учредитель — АО «НПП „Машпром“»</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="92" customHeight="1">
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="86" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Целевой</t>
@@ -1209,28 +1361,40 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>АО «ПНИТИ» Пермь</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
+          <t>АО «ПНИТИ»</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Пермь</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Портальный BMC-5131 с угловой головой : стол 5000 × 2900 мм, нагрузка 20 тонн , ходы 5100 / 3100 / 1100 мм, максимальный габарит заготовки 5000 × 2800 × 850 мм. Угловая голова — прямо под радиальные борта под углом</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>8 (342) 240-25-04 marketing@pniti.ru</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+          <t>Портальный BMC-5131 с угловой головой: стол 5000 × 2900 мм, нагрузка 20 тонн, ходы 5100 / 3100 / 1100 мм, максимальный габарит заготовки 5000 × 2800 × 850 мм. Угловая голова — прямо под радиальные борта под углом</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>8 (342) 240-25-04</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>marketing@pniti.ru</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Берут ли серию 644 детали и какой темп дадут</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="92" customHeight="1">
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="86" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Целевой</t>
@@ -1238,28 +1402,44 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ООО «МЗТМ» Магнитогорск</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr"/>
+          <t>ООО «МЗТМ»</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Магнитогорск</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Фрезерные центры: стол 4000 × 2000 мм, заготовка до 14 тонн . Расточные на порталах: стол 4000 × 3000 мм, до 60 тонн . Оба передела своим оборудованием, по массе запас семикратный</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>+7 (3519) 33-09-59 mztm74@mail.ru Производство: п. Приморский, ул. Носова, 4/1</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
+          <t>Фрезерные центры: стол 4000 × 2000 мм, заготовка до 14 тонн. Расточные на порталах: стол 4000 × 3000 мм, до 60 тонн. Оба передела своим оборудованием, по массе запас семикратный</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>+7 (3519) 33-09-59</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>mztm74@mail.ru</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Производство: п. Приморский, ул. Носова, 4/1</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Сколько у них станков на самом деле: источники расходятся втрое</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="92" customHeight="1">
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="86" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Уточнить</t>
@@ -1267,28 +1447,40 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ООО «МИАН» Златоуст</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr"/>
+          <t>ООО «МИАН»</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Златоуст</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Портальные ОЦ до 3100 × 2200 × 1000 мм до 10 тонн, расточные с ЧПУ до 10 000 × 2800 мм</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>+7 (3513) 69-02-18 , +7 (902) 866-66-20 gav@zlatmian.ru, mian2010@list.ru</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>+7 (3513) 69-02-18, +7 (902) 866-66-20</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>gav@zlatmian.ru · mian2010@list.ru</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Что с заводом после 2021 года — свежих данных в открытых источниках нет</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="92" customHeight="1">
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="86" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Целевой</t>
@@ -1296,28 +1488,40 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ООО «Эльмаш» Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr"/>
+          <t>ООО «Эльмаш»</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Портальное оборудование, зона 3200 × 1600 × 1000 мм, заготовка до 10 000 кг — деталь с приспособлением проходит втрое. Чугун и давальческая схема названы прямо</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Отдел продаж механообработки +7 (83120) 616-44 Секретарь +7 (83120) 616-40 Директор Ерохин Михаил Иванович</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Отдел продаж механообработки: +7 (83120) 616-44 · Секретарь: +7 (83120) 616-40</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Директор Ерохин Михаил Иванович</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Размер стола именно под нашу деталь: 10 тонн заявлены по группе, а не по конкретному станку. И какая схема прижима применима</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="92" customHeight="1">
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="86" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Целевой</t>
@@ -1325,28 +1529,40 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ООО Компания «Чебо» Новое Атлашево, Чувашия</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr"/>
+          <t>ООО Компания «Чебо»</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Новое Атлашево, Чувашия</t>
+        </is>
+      </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Четырёхкоординатный ОЦ; по расточному заявлено 2500 × 1500 мм, до 5 тонн</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Менеджер по механообработке Алексей Васильев, +7 (8352) 28-50-19 tvc@chebo.ru</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>+7 (8352) 28-50-19</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>tvc@chebo.ru</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Размеры по фрезерной группе — на сайте их нет</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="92" customHeight="1">
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="86" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Запасной</t>
@@ -1354,28 +1570,40 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ООО «ДжиЭрСи» Щёлково</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr"/>
+          <t>ООО «ДжиЭрСи»</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Щёлково</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Оговорка: на фрезерную группу наша ширина 1150 мм не встаёт — столы 1800 × 800 и 1800 × 630 мм. Обе серии берёт только координатно-расточной 2Е470А, стол 1400 × 2240 мм, до 2500 кг</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>8 (800) 500-63-74 zapros@1grc.ru</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>8 (800) 500-63-74</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>zapros@1grc.ru</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Чем будете фрезеровать ширину 1150 мм — на расточном плоскости не получить. И два жёстких ограничения самого 2Е470А: грузоподъёмность 2500 кг — деталь 1895 кг проходит, а вместе с приспособлением (2900–3300 кг) уже нет; наибольший диаметр сверления 40 мм при нашем нагнетательном отверстии Ø120</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="92" customHeight="1">
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="86" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Запасной</t>
@@ -1383,28 +1611,40 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ПАО «ЧКПЗ» Челябинск</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr"/>
+          <t>ПАО «ЧКПЗ»</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Челябинск</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Портальный VB-2516, горизонтальный четырёхосевой HAAS EC-2000, Skoda W200 со столом 3500 × 3500 мм до 60 тонн</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>+7 (351) 259-45-01 , +7 (351) 259-10-91 Челябинск, ул. Ф. Горелова, 12</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>+7 (351) 259-45-01, +7 (351) 259-10-91</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Челябинск, ул. Ф. Горелова, 12</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Не авансировать. Заёмные 44,3 млрд ₽, кредиторская задолженность 69,9 млрд ₽, в апреле 2026 кредитор объявил намерение банкротить</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="92" customHeight="1">
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="86" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Запасной</t>
@@ -1412,28 +1652,40 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>АО «ТЯЖМАШ» Сызрань</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr"/>
+          <t>АО «ТЯЖМАШ»</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Сызрань</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Портальные ОЦ, наибольший стол 4500 × 12 000 мм; более 100 фрезерных</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Справочная +7 (8464) 37-81-09 Маркетинг 8 800 350 81 92 market@tyazhmash.com, sale@tyazhmash.com</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Справочная: +7 (8464) 37-81-09 · Маркетинг: 8 800 350 81 92</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>market@tyazhmash.com · sale@tyazhmash.com</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="9" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Берут ли работу со стороны — открыто услуга не предлагается. В 2004 обрабатывали чужие тюбинги Ø14 м, то есть отказ не предрешён. И грузоподъёмность столов — она не опубликована</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="92" customHeight="1">
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="86" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Запасной</t>
@@ -1441,28 +1693,40 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ООО «Вариант-999» Красноярск</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr"/>
+          <t>ООО «Вариант-999»</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Красноярск</t>
+        </is>
+      </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>32 фрезерных центра, детали до 13 тонн и 1300 × 2500 × 4000 мм — по габариту и массе деталь с приспособлением проходит свободно. Но все 32 трёхосевые : радиальный борт под углом трёхосевой станок без поворотной головы одним установом не режет</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>+7 (391) 201-60-39 Осторожно: домен вариант-999.рф принадлежит другому предприятию, проверять при звонке, туда ли попал</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+          <t>32 фрезерных центра, детали до 13 тонн и 1300 × 2500 × 4000 мм — по габариту и массе деталь с приспособлением проходит свободно. Но все 32 трёхосевые: радиальный борт под углом трёхосевой станок без поворотной головы одним установом не режет</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>+7 (391) 201-60-39</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Осторожно: домен вариант-999.рф принадлежит другому предприятию, проверять при звонке, туда ли попал</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Обработка прямо в точке поставки первого заказа, крюк ноль километров — по перевозке лучший вариант из всех. Против: иск на 347,4 млн ₽, это три четверти их чистых активов, и под радиальные борта на трёхосевом нужен угловой блок с зашитым углом на каждую геометрию. Спросить, чем они режут наклонные плоскости</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="92" customHeight="1">
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="86" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Запасной</t>
@@ -1470,28 +1734,36 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>АО «Пензадизельмаш» Пенза</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr"/>
+          <t>АО «Пензадизельмаш»</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Пенза</t>
+        </is>
+      </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Обрабатывающие центры DMU 50, HEC 800, CTX gamma 3000 TC. Все опубликованные габариты меньше нашей детали</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Приёмная +7 (8412) 36-92-10 Технический директор +7 (8412) 36-93-61 Коммерческий +7 (8412) 36-94-33</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Приёмная: +7 (8412) 36-92-10 · Технический директор: +7 (8412) 36-93-61 · Коммерческий: +7 (8412) 36-94-33</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Есть ли станок под 2083 × 1150 мм. Плечо нулевое, ради этого стоит спросить. Разговор строить как обмен загрузкой</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="92" customHeight="1">
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="86" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Запасной</t>
@@ -1499,29 +1771,45 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ООО «НПО «НефтехГазМаш» Рузаевка</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr"/>
+          <t>ООО «НПО «НефтехГазМаш»</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Рузаевка</t>
+        </is>
+      </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Станки ЧПУ фрезерной и расточной группы — зона 1500 × 1000 × 1000 мм, наша длина 2083 туда не входит. Но строгальная группа берёт: детали до 4000 × 1250 × 1120 мм, включая наклонные поверхности — это прямо про радиальные борта под углом</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>+7 (83451) 6-10-32 ok_ngm@mail.ru, neftehgazmash@mail.ru Рузаевка, ул. Пионерская, 119</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Есть ли станок с ЧПУ длиннее 2083 мм. Если нет — готовы ли делать строганием и какая тогда трудоёмкость. И отдельно: строгальная берёт ширину 1250 мм , деталь 1150 — запас всего 50 мм на сторону, поэтому спросить, можно ли прижимать только по торцам : приспособление с прижимами по контуру в 1250 уже не войдёт. 116 км от Пензы — ближайший из всех , ради этого стоит спросить</t>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>+7 (83451) 6-10-32</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>ok_ngm@mail.ru · neftehgazmash@mail.ru</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Рузаевка, ул. Пионерская, 119</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Есть ли станок с ЧПУ длиннее 2083 мм. Если нет — готовы ли делать строганием и какая тогда трудоёмкость. И отдельно: строгальная берёт ширину 1250 мм, деталь 1150 — запас всего 50 мм на сторону, поэтому спросить, можно ли прижимать только по торцам: приспособление с прижимами по контуру в 1250 уже не войдёт. 116 км от Пензы — ближайший из всех, ради этого стоит спросить</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G25"/>
+  <autoFilter ref="A5:K25"/>
   <mergeCells count="1">
     <mergeCell ref="A3:G3"/>
   </mergeCells>
